--- a/data_files/2026-06/ventas/ventas 01-07.xlsx
+++ b/data_files/2026-06/ventas/ventas 01-07.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2370" windowHeight="105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="6345"/>
   </bookViews>
   <sheets>
     <sheet name="aexcel" sheetId="1" r:id="rId1"/>
